--- a/Матриця інтеграції NIST CSFv2.xlsx
+++ b/Матриця інтеграції NIST CSFv2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\користувач\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\користувач\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39A31BD7-BCE3-485A-8309-372AAF45BDA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{401B4012-A798-4CEA-9ED6-40AC707DF030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{46A9AAD0-2678-412F-B357-8B6BED3B713B}"/>
   </bookViews>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3456" uniqueCount="935">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3457" uniqueCount="935">
   <si>
     <t>Наслідок CSF (Функція, категорія або підкатегорія)</t>
   </si>
@@ -9771,7 +9771,9 @@
       <c r="AA84" s="17" t="s">
         <v>928</v>
       </c>
-      <c r="AB84" s="17"/>
+      <c r="AB84" s="17" t="s">
+        <v>929</v>
+      </c>
       <c r="AC84" s="17" t="str">
         <f>IF(OR(Table2[[#This Row],[Базовий профіль - ДССЗЗІ]]&lt;&gt;"",Table2[[#This Row],[Оператори критичної інфраструктури та власники або розпорядники ОКІІ І та ІІ категорій критичності]]&lt;&gt;"",Table2[[#This Row],[Оператори критичної інфраструктури та власники або розпорядники ОКІІ ІІІ та IV категорій критичності]]&lt;&gt;"",Table2[[#This Row],[Органи державної влади, інші державні органи, органи місцевого самоврядування, державні підприємства, установи та організації, які є власниками або розпорядниками систем, в яких обробляються державні інформаційні ресурси]]&lt;&gt;"",Table2[[#This Row],[Органи державної влади, інші державні органи, органи місцевого самоврядування, державні підприємства, установи та організації, які є власниками або розпорядниками систем, в яких обробляється інформація з обмеженим доступом, вимога щодо захисту якої встано]]&lt;&gt;""),"Так","")</f>
         <v>Так</v>
@@ -11071,7 +11073,7 @@
       <formula>NOT(ISERROR(SEARCH("No",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:F107 J2:J107" xr:uid="{B1155E60-440F-411B-A380-5ED7FF601485}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
